--- a/code/data/numbers/w0wacdm-fixed.xlsx
+++ b/code/data/numbers/w0wacdm-fixed.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/852b2bada49559ee/code_final/data/numbers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\28943\OneDrive\NeutrinoForecast_J-PAS_PFS\code\data\numbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_085D38BF95627E0F6235547658668E7992279C9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4189575-74A7-4C9B-B02C-3A5F078B6732}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343AC3B2-016E-438A-A783-6924E0104E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="437" windowWidth="18720" windowHeight="11434" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -153,14 +158,14 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -471,9 +476,9 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="9.23046875" style="5"/>
-    <col min="4" max="4" width="9.23046875" style="6"/>
-    <col min="5" max="6" width="9.23046875" style="5"/>
+    <col min="2" max="3" width="9.23046875" style="3"/>
+    <col min="4" max="4" width="9.23046875" style="5"/>
+    <col min="5" max="6" width="9.23046875" style="3"/>
     <col min="7" max="8" width="9.23046875" style="7"/>
     <col min="9" max="9" width="9.23046875" style="9"/>
   </cols>
@@ -485,7 +490,7 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -494,10 +499,10 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="8" t="s">
@@ -508,48 +513,48 @@
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5">
-        <v>7.3655026246337657E-2</v>
-      </c>
-      <c r="C2" s="5">
-        <v>6.999067621937631E-2</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1.0777319742822179E-2</v>
-      </c>
-      <c r="E2" s="5">
-        <v>6.5748502817060919E-2</v>
-      </c>
-      <c r="F2" s="5">
-        <v>2.0294247084870301E-3</v>
+      <c r="B2" s="3">
+        <v>8.1348924227673175E-2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7.7172993209789334E-2</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.190469355983702E-2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7.2049604472197465E-2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.9818378818899189E-3</v>
       </c>
       <c r="G2" s="7">
-        <v>0.13828182534004119</v>
+        <v>0.13437066059865199</v>
       </c>
       <c r="H2" s="7">
-        <v>0.53043351310542297</v>
+        <v>0.54610156101265717</v>
       </c>
       <c r="I2" s="9">
-        <v>1.4906128116910871</v>
+        <v>1.468747624215442</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5">
-        <v>2.089273279950192E-2</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="3">
+        <v>2.0892732799502021E-2</v>
+      </c>
+      <c r="C3" s="3">
         <v>3.3774688094691967E-2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>8.6733399644891348E-3</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>2.4415513910606011E-2</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>4.2226247198859597E-2</v>
       </c>
       <c r="G3" s="7">
@@ -566,23 +571,23 @@
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
-        <v>3.5127866874487858E-2</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="3">
+        <v>3.512786687448774E-2</v>
+      </c>
+      <c r="C4" s="3">
         <v>4.6102825372574492E-2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>1.189700386572571E-2</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>3.9930706042750452E-2</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>6.6376969434849234E-2</v>
       </c>
       <c r="G4" s="7">
-        <v>0.42501131083782601</v>
+        <v>0.42501131083782351</v>
       </c>
       <c r="H4" s="7">
         <v>0.20344581621240951</v>
@@ -595,19 +600,19 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>1.97473879974495E-2</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>0.13543737919041721</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>2.8200128968153899E-2</v>
       </c>
-      <c r="E5" s="5">
-        <v>0.1227098805692953</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="3">
+        <v>0.1227098805692957</v>
+      </c>
+      <c r="F5" s="3">
         <v>0.11556090841067911</v>
       </c>
       <c r="G5" s="7">
@@ -624,19 +629,19 @@
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5">
-        <v>1.5853945774354901E-2</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="3">
+        <v>1.5853945774354911E-2</v>
+      </c>
+      <c r="C6" s="3">
         <v>3.4300168608464757E-2</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>8.4225277778259885E-3</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>4.5630876830251098E-2</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>5.4860378822865083E-2</v>
       </c>
       <c r="G6" s="7">
@@ -653,19 +658,19 @@
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>1.0073251131867959E-2</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <v>1.3725079684273009E-2</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>3.9815803835823666E-3</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>1.78882012732622E-2</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <v>1.8477169093621921E-2</v>
       </c>
       <c r="G7" s="7">
@@ -682,55 +687,55 @@
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5">
-        <v>7.2453290614357679E-3</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.1423363855223649E-2</v>
-      </c>
-      <c r="D8" s="6">
-        <v>3.225803686413693E-3</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="B8" s="3">
+        <v>7.2453290614357584E-3</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.142336385522362E-2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3.2258036864136791E-3</v>
+      </c>
+      <c r="E8" s="3">
         <v>1.609745100645105E-2</v>
       </c>
-      <c r="F8" s="5">
-        <v>1.4666196130321491E-2</v>
+      <c r="F8" s="3">
+        <v>1.466619613032146E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>0.1963013209130359</v>
+        <v>0.19630132091303609</v>
       </c>
       <c r="H8" s="7">
-        <v>9.1423400161520285E-2</v>
+        <v>9.1423400161519827E-2</v>
       </c>
       <c r="I8" s="9">
-        <v>0.40291256094088501</v>
+        <v>0.40291256094088279</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>7.1989329107590922E-3</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>9.2989032900076627E-3</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>2.6194873943998051E-3</v>
       </c>
-      <c r="E9" s="5">
-        <v>1.5142904945156389E-2</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="3">
+        <v>1.514290494515644E-2</v>
+      </c>
+      <c r="F9" s="3">
         <v>2.0303247234603861E-2</v>
       </c>
       <c r="G9" s="7">
         <v>0.22556412463149819</v>
       </c>
       <c r="H9" s="7">
-        <v>4.5846102771965741E-2</v>
+        <v>4.5846102771965713E-2</v>
       </c>
       <c r="I9" s="9">
         <v>0.26802651211462791</v>
@@ -740,58 +745,58 @@
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5">
-        <v>2.692492045753149E-3</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2.968472057015655E-3</v>
-      </c>
-      <c r="D10" s="6">
-        <v>4.1476185973330601E-4</v>
-      </c>
-      <c r="E10" s="5">
-        <v>5.8675183430304699E-3</v>
-      </c>
-      <c r="F10" s="5">
-        <v>1.6928048589322511E-3</v>
+      <c r="B10" s="3">
+        <v>2.693660655593887E-3</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.9454777598169708E-3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4.1887118661471269E-4</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.8585264607988168E-3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.659320340288492E-3</v>
       </c>
       <c r="G10" s="7">
-        <v>5.3569358601234802E-2</v>
+        <v>5.2438960468030107E-2</v>
       </c>
       <c r="H10" s="7">
-        <v>4.3537334781141877E-2</v>
+        <v>4.3672652735414208E-2</v>
       </c>
       <c r="I10" s="9">
-        <v>0.17083278791076259</v>
+        <v>0.16998855007516661</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5">
-        <v>2.12144082797167E-3</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2.265704696394514E-3</v>
-      </c>
-      <c r="D11" s="6">
-        <v>3.2396091998256651E-4</v>
-      </c>
-      <c r="E11" s="5">
-        <v>4.7844068304937742E-3</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1.598284660854148E-3</v>
+      <c r="B11" s="3">
+        <v>2.1192647231293919E-3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.2580168436305359E-3</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3.262468872232489E-4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.7929479271527891E-3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.5703215831356239E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>4.1546382864861217E-2</v>
+        <v>4.1100919263709942E-2</v>
       </c>
       <c r="H11" s="7">
-        <v>2.867986814820982E-2</v>
+        <v>2.875596738750277E-2</v>
       </c>
       <c r="I11" s="9">
-        <v>9.9500881339431857E-2</v>
+        <v>9.9691717967630711E-2</v>
       </c>
     </row>
   </sheetData>
